--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
